--- a/Stata 4/Dataset_IDcard.xlsx
+++ b/Stata 4/Dataset_IDcard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f66ff72783ca365e/Experimental Design/Stata 4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f66ff72783ca365e/Experimental Design/Peer Review 2/ppol6818-spring2026/Stata 4/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_24F67D543A8413A3DE567FC04CA6F64DA24E87FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18170" yWindow="2960" windowWidth="15870" windowHeight="16470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mc_sim_results" sheetId="1" r:id="rId1"/>
@@ -388,14 +388,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -714,7 +714,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7"/>
@@ -728,7 +728,7 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7"/>
@@ -740,14 +740,14 @@
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="7"/>
@@ -757,7 +757,7 @@
       <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="7"/>
@@ -769,7 +769,7 @@
       <c r="E9" s="3">
         <v>2500</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="7"/>
@@ -789,7 +789,7 @@
       <c r="E12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G12" s="7"/>
@@ -804,7 +804,7 @@
       <c r="E13" s="3">
         <v>2500</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="7"/>
@@ -818,11 +818,11 @@
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="7"/>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="7"/>
@@ -832,11 +832,11 @@
       <c r="B17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="7"/>
@@ -846,11 +846,11 @@
       <c r="B18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="7"/>
@@ -860,11 +860,11 @@
       <c r="B19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="8" t="s">
         <v>29</v>
       </c>
       <c r="F19" s="7"/>
@@ -874,11 +874,11 @@
       <c r="B20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D20" s="7"/>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F20" s="7"/>
@@ -888,11 +888,11 @@
       <c r="B21" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="8" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="7"/>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F21" s="7"/>
@@ -902,11 +902,11 @@
       <c r="B22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="8" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="7"/>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="8" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="7"/>
@@ -921,11 +921,11 @@
       <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="7"/>
@@ -935,11 +935,11 @@
       <c r="B30" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D30" s="7"/>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="8" t="s">
         <v>41</v>
       </c>
       <c r="F30" s="7"/>
@@ -947,17 +947,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E19:G19"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="E30:G30"/>
@@ -973,6 +962,17 @@
     <mergeCell ref="E22:G22"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -997,7 +997,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7"/>
@@ -1011,7 +1011,7 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D5" s="7"/>
@@ -1023,14 +1023,14 @@
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>43</v>
       </c>
       <c r="B8" s="7"/>
@@ -1040,7 +1040,7 @@
       <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="7"/>
@@ -1052,7 +1052,7 @@
       <c r="E9" s="3">
         <v>31</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="7"/>
@@ -1072,7 +1072,7 @@
       <c r="E12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G12" s="7"/>
@@ -1087,7 +1087,7 @@
       <c r="E13" s="3">
         <v>31</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="9" t="s">
         <v>46</v>
       </c>
       <c r="G13" s="7"/>
@@ -1101,11 +1101,11 @@
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="7"/>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="7"/>
@@ -1115,11 +1115,11 @@
       <c r="B17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="8" t="s">
         <v>49</v>
       </c>
       <c r="F17" s="7"/>
@@ -1129,11 +1129,11 @@
       <c r="B18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="8" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="7"/>
@@ -1143,11 +1143,11 @@
       <c r="B19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F19" s="7"/>
@@ -1157,11 +1157,11 @@
       <c r="B20" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="8" t="s">
         <v>57</v>
       </c>
       <c r="D20" s="7"/>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="8" t="s">
         <v>58</v>
       </c>
       <c r="F20" s="7"/>
@@ -1176,11 +1176,11 @@
       <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="7"/>
@@ -1188,12 +1188,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:G16"/>
@@ -1204,10 +1198,16 @@
     <mergeCell ref="E29:G29"/>
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="D7:F7"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1232,7 +1232,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7"/>
@@ -1246,7 +1246,7 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="7"/>
@@ -1258,14 +1258,14 @@
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="B8" s="7"/>
@@ -1275,7 +1275,7 @@
       <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="7"/>
@@ -1287,7 +1287,7 @@
       <c r="E9" s="3">
         <v>206559</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>62</v>
       </c>
       <c r="G9" s="7"/>
@@ -1307,7 +1307,7 @@
       <c r="E12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G12" s="7"/>
@@ -1322,7 +1322,7 @@
       <c r="E13" s="3">
         <v>31</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="9" t="s">
         <v>64</v>
       </c>
       <c r="G13" s="7"/>
@@ -1336,11 +1336,11 @@
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="7"/>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="7"/>
@@ -1350,11 +1350,11 @@
       <c r="B17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>66</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="8" t="s">
         <v>67</v>
       </c>
       <c r="F17" s="7"/>
@@ -1364,11 +1364,11 @@
       <c r="B18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>63</v>
       </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="8" t="s">
         <v>69</v>
       </c>
       <c r="F18" s="7"/>
@@ -1383,11 +1383,11 @@
       <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="7"/>
@@ -1397,11 +1397,11 @@
       <c r="B30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="8" t="s">
         <v>63</v>
       </c>
       <c r="D30" s="7"/>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="8" t="s">
         <v>70</v>
       </c>
       <c r="F30" s="7"/>
@@ -1409,6 +1409,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:G30"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="E17:G17"/>
@@ -1425,8 +1427,6 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:G30"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1451,7 +1451,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7"/>
@@ -1465,7 +1465,7 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="7"/>
@@ -1477,14 +1477,14 @@
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>43</v>
       </c>
       <c r="B8" s="7"/>
@@ -1494,7 +1494,7 @@
       <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="7"/>
@@ -1506,7 +1506,7 @@
       <c r="E9" s="3">
         <v>25</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>72</v>
       </c>
       <c r="G9" s="7"/>
@@ -1526,7 +1526,7 @@
       <c r="E12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G12" s="7"/>
@@ -1541,7 +1541,7 @@
       <c r="E13" s="3">
         <v>25</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="9" t="s">
         <v>74</v>
       </c>
       <c r="G13" s="7"/>
@@ -1555,11 +1555,11 @@
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="7"/>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="7"/>
@@ -1569,11 +1569,11 @@
       <c r="B17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="8" t="s">
         <v>75</v>
       </c>
       <c r="F17" s="7"/>
@@ -1583,11 +1583,11 @@
       <c r="B18" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="8" t="s">
         <v>78</v>
       </c>
       <c r="F18" s="7"/>
@@ -1597,11 +1597,11 @@
       <c r="B19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="8" t="s">
         <v>80</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="8" t="s">
         <v>81</v>
       </c>
       <c r="F19" s="7"/>
@@ -1611,11 +1611,11 @@
       <c r="B20" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="8" t="s">
         <v>83</v>
       </c>
       <c r="D20" s="7"/>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="8" t="s">
         <v>84</v>
       </c>
       <c r="F20" s="7"/>
@@ -1630,11 +1630,11 @@
       <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="7"/>
@@ -1642,12 +1642,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:G16"/>
@@ -1658,10 +1652,16 @@
     <mergeCell ref="E29:G29"/>
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="D7:F7"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1686,7 +1686,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7"/>
@@ -1700,7 +1700,7 @@
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>85</v>
       </c>
       <c r="D5" s="7"/>
@@ -1712,14 +1712,14 @@
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>43</v>
       </c>
       <c r="B8" s="7"/>
@@ -1729,7 +1729,7 @@
       <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="7"/>
@@ -1741,7 +1741,7 @@
       <c r="E9" s="3">
         <v>32</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>86</v>
       </c>
       <c r="G9" s="7"/>
@@ -1761,7 +1761,7 @@
       <c r="E12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G12" s="7"/>
@@ -1776,7 +1776,7 @@
       <c r="E13" s="3">
         <v>31</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="9" t="s">
         <v>88</v>
       </c>
       <c r="G13" s="7"/>
@@ -1790,11 +1790,11 @@
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="7"/>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="7"/>
@@ -1804,11 +1804,11 @@
       <c r="B17" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>90</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="8" t="s">
         <v>91</v>
       </c>
       <c r="F17" s="7"/>
@@ -1818,11 +1818,11 @@
       <c r="B18" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D18" s="7"/>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="8" t="s">
         <v>93</v>
       </c>
       <c r="F18" s="7"/>
@@ -1832,11 +1832,11 @@
       <c r="B19" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="8" t="s">
         <v>96</v>
       </c>
       <c r="F19" s="7"/>
@@ -1851,11 +1851,11 @@
       <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="7"/>
@@ -1863,6 +1863,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:G29"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C5:G5"/>
@@ -1879,8 +1881,6 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:G29"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
